--- a/broker_forms/032_investment_management_quote_form--broker_forms.xlsx
+++ b/broker_forms/032_investment_management_quote_form--broker_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>investment_frequency</t>
+          <t>investment_frequency_2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Investment Frequency</t>
+          <t>Investment Frequency 2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>investment_amount</t>
+          <t>investment_amount_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Investment Amount</t>
+          <t>Investment Amount 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>investment_return</t>
+          <t>investment_return_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Investment Return</t>
+          <t>Investment Return 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>investment_duration</t>
+          <t>investment_duration_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Investment Duration</t>
+          <t>Investment Duration 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>asset_allocation</t>
+          <t>asset_allocation_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Asset Allocation</t>
+          <t>Asset Allocation 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>investment_objective</t>
+          <t>investment_objective_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Investment Objective</t>
+          <t>Investment Objective 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>contact_email</t>
+          <t>contact_email_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Contact Email 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1003,12 +1003,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>contact_phone</t>
+          <t>contact_phone_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Contact Phone 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1296,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>investment_frequency_choices</t>
+          <t>investment_frequency_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1483,7 +1483,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>asset_allocation_choices</t>
+          <t>asset_allocation_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1500,7 +1500,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>asset_allocation_choices</t>
+          <t>asset_allocation_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1517,7 +1517,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>asset_allocation_choices</t>
+          <t>asset_allocation_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1534,7 +1534,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>asset_allocation_choices</t>
+          <t>asset_allocation_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1551,7 +1551,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>investment_objective_choices</t>
+          <t>investment_objective_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1568,7 +1568,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>investment_objective_choices</t>
+          <t>investment_objective_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1585,7 +1585,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>investment_objective_choices</t>
+          <t>investment_objective_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
